--- a/public/crawlability-qmd-september-2026.xlsx
+++ b/public/crawlability-qmd-september-2026.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של qmd ב-SE Ranking (הסריקה האחרונה: 2026-04-03).</t>
+          <t>להריץ מחדש את ה-Website Audit של qmd ב-SE Ranking (הסריקה האחרונה: 2026-04-03); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-qmd-september-2026.xlsx
+++ b/public/crawlability-qmd-september-2026.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>קישורי Cloudflare (ללא טיפול)</t>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">

--- a/public/crawlability-qmd-september-2026.xlsx
+++ b/public/crawlability-qmd-september-2026.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של qmd ב-SE Ranking (הסריקה האחרונה: 2026-04-03); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של qmd ב-SE Ranking; הסריקה האחרונה: 2026-04-03.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-qmd-september-2026.xlsx
+++ b/public/crawlability-qmd-september-2026.xlsx
@@ -75,13 +75,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -470,21 +470,6 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>פעולה</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של qmd ב-SE Ranking; הסריקה האחרונה: 2026-04-03.</t>
         </is>
       </c>
     </row>
@@ -573,44 +558,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/cdn-cgi/l/email-protection</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/locations/
 https://qmd.net/contact/</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>קישור הגנת דוא"ל של Cloudflare (cdn-cgi). גוגל מתעלם מכתובות cdn-cgi; לא נדרש טיפול. ניתן לבטל את Email Address Obfuscation ב-Cloudflare כדי שהסורקים לא ידווחו על כך.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -659,372 +644,372 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>robots.txt</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>קוד תשובה</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>robots.txt</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/sitemap_index.xml</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>robots.txt</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>סורקי AI חסומים</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>אין</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>robots.txt</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>סורקי חיפוש חסומים</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>אין</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>מפת אתר</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/sitemap_index.xml</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>אינדקס</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>מפת אתר</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/page-sitemap.xml</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>8 כתובות</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>מפת אתר</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/product-sitemap.xml</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>17 כתובות</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>מפת אתר</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/sitemap.xml</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>אינדקס</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>מפת אתר</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/wp-sitemap.xml</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>אינדקס</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>מפת אתר</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/post-sitemap.xml</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>1 כתובות</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>מפת אתר</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>כתובות ייחודיות</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>qmd.net: 26</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/ (0 הפניות)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>http://qmd.net/</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/ (1 הפניות)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>https://www.qmd.net/</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/ (1 הפניות)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>http://www.qmd.net/</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/ (2 הפניות)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>עמוד הבית</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>meta robots</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>index, follow, max-image-preview:large, max-snippet:-1, max-video-preview:-1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>עמוד הבית</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>X-Robots-Tag</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>עמוד הבית</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>canonical</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>https://qmd.net/</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1063,85 +1048,85 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>סריקת Screaming Frog (קובץ הלקוח)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>23.09.2026</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>כל עמודי ה-HTML עם קוד שונה מ-200</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>בדיקה חיה (curl, User-agent של Googlebot)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>robots.txt, מפות אתר, גרסאות דומיין, אימות מחדש של כל כתובת שגיאה, תת-דומיינים</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>SE Ranking Website Audit API</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>לפי תאריך הסריקה בפרויקט</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>ממצאי סטטוס ועמודי מקור (Found links)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Google Search Console API</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>מצב מפות האתר בנכסים שבגישתנו</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>crt.sh + DNS</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>27.09.2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>איתור תת-דומיינים</t>
         </is>
